--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260707.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260707.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>904,244,000</t>
+          <t>909,044,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.53%</t>
+          <t>10.55%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.71%</t>
+          <t>6.01%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.02%</t>
+          <t>4.75%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>4.22%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>3.49%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.33%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.30%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.29%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
@@ -853,51 +853,51 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>31,116,000</t>
+          <t>31,256,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>28,430,000</t>
+          <t>134,019,945</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>134,019,945</t>
+          <t>343,589,964</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,176 +909,176 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>343,589,964</t>
+          <t>226,166,516</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.61%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>132,597,000</t>
+          <t>28,430,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>226,166,516</t>
+          <t>150,152,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>149,092,000</t>
+          <t>133,147,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>191,517,000</t>
+          <t>1,696</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,516</t>
+          <t>191,517,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>100,367,000</t>
+          <t>371,675,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>371,675,000</t>
+          <t>100,847,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>81,388,000</t>
+          <t>82,168,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>279,366,000</t>
+          <t>281,366,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>14,603,000</t>
+          <t>14,683,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>7,043,565,312</t>
+          <t>9,628,447,680</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>7,092,270,248</t>
+          <t>3,270,528,792</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-66,264,382</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
